--- a/data/trans_orig/P70B_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P70B_2023-Habitat-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según como se adapta su horario laboral a sus compromisos sociales y familiares fuera del trabajo en 2023</t>
+          <t>Población según como se adapta su horario laboral a sus compromisos sociales y familiares fuera del trabajo en 2023 (tasa de respuesta: 99,54%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7714</t>
+          <t>7481</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>24512</t>
+          <t>23827</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1281</t>
+          <t>1372</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7891</t>
+          <t>7756</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>10415</t>
+          <t>10435</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>28046</t>
+          <t>28327</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,8%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>32419</t>
+          <t>34955</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>60517</t>
+          <t>62260</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>10,46%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>18,1%</t>
+          <t>18,62%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>27230</t>
+          <t>26711</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>46180</t>
+          <t>46290</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>10,44%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>18,04%</t>
+          <t>18,09%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>66953</t>
+          <t>65431</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>100424</t>
+          <t>100968</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>11,09%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>17,01%</t>
+          <t>17,11%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>180720</t>
+          <t>181052</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>221684</t>
+          <t>221311</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>54,06%</t>
+          <t>54,16%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>66,31%</t>
+          <t>66,2%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>138114</t>
+          <t>137712</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>164813</t>
+          <t>165520</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>53,96%</t>
+          <t>53,8%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>64,39%</t>
+          <t>64,67%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>331336</t>
+          <t>329018</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>376807</t>
+          <t>377530</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>56,13%</t>
+          <t>55,74%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>63,84%</t>
+          <t>63,96%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>57789</t>
+          <t>58298</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>91745</t>
+          <t>92630</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>17,29%</t>
+          <t>17,44%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>27,44%</t>
+          <t>27,71%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>54252</t>
+          <t>53077</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>76969</t>
+          <t>77844</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>21,2%</t>
+          <t>20,74%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>30,07%</t>
+          <t>30,41%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>117697</t>
+          <t>117129</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>159454</t>
+          <t>159632</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>19,94%</t>
+          <t>19,84%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>27,01%</t>
+          <t>27,04%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6021</t>
+          <t>5948</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>33361</t>
+          <t>32701</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>4416</t>
+          <t>4016</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>13554</t>
+          <t>13229</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>13909</t>
+          <t>12949</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>42565</t>
+          <t>39669</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,29%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>29879</t>
+          <t>31836</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>119179</t>
+          <t>120537</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>14,8%</t>
+          <t>14,97%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>40105</t>
+          <t>41025</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>64555</t>
+          <t>64410</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>16,1%</t>
+          <t>16,07%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>68630</t>
+          <t>58965</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>173444</t>
+          <t>172388</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>14,29%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>493675</t>
+          <t>491245</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>715481</t>
+          <t>711113</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>61,3%</t>
+          <t>61,0%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>88,84%</t>
+          <t>88,3%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>239859</t>
+          <t>240205</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>273647</t>
+          <t>275680</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>59,83%</t>
+          <t>59,92%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>68,26%</t>
+          <t>68,77%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>749644</t>
+          <t>747360</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1018053</t>
+          <t>1028111</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>62,15%</t>
+          <t>61,96%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>84,4%</t>
+          <t>85,23%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>46149</t>
+          <t>49871</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>175120</t>
+          <t>174742</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>21,74%</t>
+          <t>21,7%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>70582</t>
+          <t>68962</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>99713</t>
+          <t>99688</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,7 +1688,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>17,61%</t>
+          <t>17,2%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>111660</t>
+          <t>102234</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>261032</t>
+          <t>261558</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>21,64%</t>
+          <t>21,68%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>861</t>
+          <t>867</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>8858</t>
+          <t>8664</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3984</t>
+          <t>3852</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>14545</t>
+          <t>14730</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6174</t>
+          <t>6348</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>19705</t>
+          <t>18439</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,73%</t>
         </is>
       </c>
     </row>
@@ -1981,12 +1981,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>31532</t>
+          <t>31978</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>63957</t>
+          <t>65877</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1996,12 +1996,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>18,19%</t>
+          <t>18,74%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2016,12 +2016,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>23729</t>
+          <t>23950</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>47063</t>
+          <t>47033</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2031,12 +2031,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>14,54%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2051,12 +2051,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>62194</t>
+          <t>61343</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>102152</t>
+          <t>103042</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2066,12 +2066,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>15,13%</t>
+          <t>15,26%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>191255</t>
+          <t>191638</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>232655</t>
+          <t>233429</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>54,4%</t>
+          <t>54,51%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>66,18%</t>
+          <t>66,4%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>185007</t>
+          <t>183889</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>242549</t>
+          <t>243069</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>57,18%</t>
+          <t>56,84%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>74,97%</t>
+          <t>75,13%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>386936</t>
+          <t>387537</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>458687</t>
+          <t>457876</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>57,32%</t>
+          <t>57,41%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>67,95%</t>
+          <t>67,83%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>73659</t>
+          <t>74374</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>110922</t>
+          <t>111833</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>20,95%</t>
+          <t>21,16%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>31,55%</t>
+          <t>31,81%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>51110</t>
+          <t>49283</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>91937</t>
+          <t>91231</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>15,23%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>28,42%</t>
+          <t>28,2%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>136541</t>
+          <t>137146</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>190089</t>
+          <t>191169</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>20,23%</t>
+          <t>20,32%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>28,16%</t>
+          <t>28,32%</t>
         </is>
       </c>
     </row>
@@ -2437,12 +2437,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6290</t>
+          <t>6235</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>18947</t>
+          <t>18657</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2452,12 +2452,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2472,12 +2472,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>8664</t>
+          <t>9023</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>35204</t>
+          <t>37121</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2487,12 +2487,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2507,12 +2507,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>17937</t>
+          <t>17344</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>48901</t>
+          <t>46341</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2522,12 +2522,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>4,86%</t>
         </is>
       </c>
     </row>
@@ -2550,12 +2550,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>32462</t>
+          <t>33065</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>59460</t>
+          <t>59532</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2565,12 +2565,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>12,59%</t>
+          <t>12,61%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2585,12 +2585,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>26802</t>
+          <t>25769</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>59095</t>
+          <t>58161</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2600,12 +2600,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>12,08%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2620,12 +2620,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>65313</t>
+          <t>68215</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>109328</t>
+          <t>110154</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2635,12 +2635,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>11,55%</t>
         </is>
       </c>
     </row>
@@ -2663,12 +2663,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>238273</t>
+          <t>235240</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>282243</t>
+          <t>279458</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2678,12 +2678,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>50,46%</t>
+          <t>49,82%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>59,77%</t>
+          <t>59,18%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2698,12 +2698,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>140828</t>
+          <t>141580</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>267885</t>
+          <t>268909</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>29,24%</t>
+          <t>29,4%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>55,63%</t>
+          <t>55,84%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>380096</t>
+          <t>376962</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>533085</t>
+          <t>533523</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>39,85%</t>
+          <t>39,52%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>55,89%</t>
+          <t>55,94%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>132672</t>
+          <t>135765</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>177762</t>
+          <t>180233</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>28,1%</t>
+          <t>28,75%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>37,65%</t>
+          <t>38,17%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>143050</t>
+          <t>142158</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>300780</t>
+          <t>303625</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>29,7%</t>
+          <t>29,52%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>62,46%</t>
+          <t>63,05%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>296959</t>
+          <t>295871</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>500095</t>
+          <t>490998</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>31,13%</t>
+          <t>31,02%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>52,43%</t>
+          <t>51,48%</t>
         </is>
       </c>
     </row>
@@ -3006,12 +3006,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>29662</t>
+          <t>27930</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>64621</t>
+          <t>62642</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3021,12 +3021,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3041,12 +3041,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>26720</t>
+          <t>26185</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>58279</t>
+          <t>61858</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3056,12 +3056,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3076,12 +3076,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>62709</t>
+          <t>61724</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>106336</t>
+          <t>106059</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3091,7 +3091,7 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
@@ -3119,12 +3119,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>142719</t>
+          <t>138148</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>259661</t>
+          <t>261414</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3134,12 +3134,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>13,22%</t>
+          <t>13,31%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3154,12 +3154,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>141400</t>
+          <t>139382</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>195911</t>
+          <t>195893</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3169,7 +3169,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3189,12 +3189,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>298039</t>
+          <t>301128</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>433254</t>
+          <t>433433</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3204,7 +3204,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>8,79%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -3232,12 +3232,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1151413</t>
+          <t>1149872</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1485142</t>
+          <t>1541874</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3247,12 +3247,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>58,64%</t>
+          <t>58,56%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>75,64%</t>
+          <t>78,53%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3267,12 +3267,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>718174</t>
+          <t>692169</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>899564</t>
+          <t>901657</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>49,12%</t>
+          <t>47,35%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>61,53%</t>
+          <t>61,67%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3302,12 +3302,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1966278</t>
+          <t>1955952</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>2344802</t>
+          <t>2380011</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>57,4%</t>
+          <t>57,1%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>68,45%</t>
+          <t>69,48%</t>
         </is>
       </c>
     </row>
@@ -3345,12 +3345,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>300865</t>
+          <t>276008</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>515387</t>
+          <t>512482</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3360,12 +3360,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>15,32%</t>
+          <t>14,06%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>26,25%</t>
+          <t>26,1%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>355791</t>
+          <t>357222</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>568702</t>
+          <t>594142</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3395,12 +3395,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>24,34%</t>
+          <t>24,43%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>38,9%</t>
+          <t>40,64%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>698987</t>
+          <t>686233</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>997183</t>
+          <t>1003424</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3430,12 +3430,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>20,41%</t>
+          <t>20,03%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>29,11%</t>
+          <t>29,29%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P70B_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P70B_2023-Habitat-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>14025</t>
+          <t>14382</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7481</t>
+          <t>7991</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>23827</t>
+          <t>24881</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>3507</t>
+          <t>4401</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1372</t>
+          <t>1775</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7756</t>
+          <t>9785</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>17533</t>
+          <t>18783</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>10435</t>
+          <t>11735</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>28327</t>
+          <t>29675</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,6%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>46149</t>
+          <t>47737</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>34955</t>
+          <t>35331</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>62260</t>
+          <t>63378</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>12,97%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>18,62%</t>
+          <t>17,22%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>35997</t>
+          <t>37735</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>26711</t>
+          <t>28837</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>46290</t>
+          <t>49563</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>14,06%</t>
+          <t>13,65%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>18,09%</t>
+          <t>17,93%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>82146</t>
+          <t>85472</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>65431</t>
+          <t>70065</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>100968</t>
+          <t>102741</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>13,26%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>10,87%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>17,11%</t>
+          <t>15,94%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>201320</t>
+          <t>221210</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>181052</t>
+          <t>198601</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>221311</t>
+          <t>242716</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>60,22%</t>
+          <t>60,09%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>54,16%</t>
+          <t>53,95%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>66,2%</t>
+          <t>65,93%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>152040</t>
+          <t>163932</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>137712</t>
+          <t>147768</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>165520</t>
+          <t>177058</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>59,4%</t>
+          <t>59,3%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>53,8%</t>
+          <t>53,45%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>64,67%</t>
+          <t>64,04%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>353360</t>
+          <t>385142</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>329018</t>
+          <t>359055</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>377530</t>
+          <t>410002</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>59,86%</t>
+          <t>59,75%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>55,74%</t>
+          <t>55,7%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>63,96%</t>
+          <t>63,61%</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>72814</t>
+          <t>84786</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>58298</t>
+          <t>67775</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>92630</t>
+          <t>106408</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>21,78%</t>
+          <t>23,03%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>17,44%</t>
+          <t>18,41%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>27,71%</t>
+          <t>28,91%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>64410</t>
+          <t>70400</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>53077</t>
+          <t>58946</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>77844</t>
+          <t>84916</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>25,16%</t>
+          <t>25,46%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20,74%</t>
+          <t>21,32%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>30,41%</t>
+          <t>30,71%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>137224</t>
+          <t>155186</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>117129</t>
+          <t>131767</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>159632</t>
+          <t>180460</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>23,25%</t>
+          <t>24,08%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>19,84%</t>
+          <t>20,44%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>27,04%</t>
+          <t>28,0%</t>
         </is>
       </c>
     </row>
@@ -1177,17 +1177,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>334309</t>
+          <t>368115</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>334309</t>
+          <t>368115</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>334309</t>
+          <t>368115</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1212,17 +1212,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>255954</t>
+          <t>276468</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>255954</t>
+          <t>276468</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>255954</t>
+          <t>276468</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1247,17 +1247,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>590263</t>
+          <t>644583</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>590263</t>
+          <t>644583</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>590263</t>
+          <t>644583</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1294,32 +1294,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>18088</t>
+          <t>18945</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5948</t>
+          <t>10594</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>32701</t>
+          <t>30966</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1329,32 +1329,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>7967</t>
+          <t>9056</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>4016</t>
+          <t>4556</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>13229</t>
+          <t>14859</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>26055</t>
+          <t>28000</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>12949</t>
+          <t>18789</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>39669</t>
+          <t>41863</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,89%</t>
         </is>
       </c>
     </row>
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>76732</t>
+          <t>82471</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>31836</t>
+          <t>63872</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>120537</t>
+          <t>107218</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>13,14%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>10,18%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>14,97%</t>
+          <t>17,08%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>51862</t>
+          <t>57715</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>41025</t>
+          <t>46390</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>64410</t>
+          <t>71455</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>12,87%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>10,34%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>16,07%</t>
+          <t>15,93%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>128594</t>
+          <t>140186</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>58965</t>
+          <t>116642</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>172388</t>
+          <t>167083</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>13,03%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>14,29%</t>
+          <t>15,53%</t>
         </is>
       </c>
     </row>
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>594525</t>
+          <t>394820</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>491245</t>
+          <t>366355</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>711113</t>
+          <t>422042</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>73,82%</t>
+          <t>62,9%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>61,0%</t>
+          <t>58,37%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>88,3%</t>
+          <t>67,24%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>257220</t>
+          <t>289053</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>240205</t>
+          <t>269037</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>275680</t>
+          <t>308886</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>64,16%</t>
+          <t>64,45%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>59,92%</t>
+          <t>59,99%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>68,77%</t>
+          <t>68,87%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>851745</t>
+          <t>683873</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>747360</t>
+          <t>648031</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1028111</t>
+          <t>715348</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>70,61%</t>
+          <t>63,55%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>61,96%</t>
+          <t>60,22%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>85,23%</t>
+          <t>66,47%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>116013</t>
+          <t>131435</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>49871</t>
+          <t>107134</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>174742</t>
+          <t>156906</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>14,41%</t>
+          <t>20,94%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>17,07%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>21,7%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>83842</t>
+          <t>92679</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>68962</t>
+          <t>77514</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>99688</t>
+          <t>112063</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>20,91%</t>
+          <t>20,66%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>17,28%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>24,87%</t>
+          <t>24,99%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>199855</t>
+          <t>224114</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>102234</t>
+          <t>196560</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>261558</t>
+          <t>256437</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>16,57%</t>
+          <t>20,83%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>18,26%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>21,68%</t>
+          <t>23,83%</t>
         </is>
       </c>
     </row>
@@ -1746,17 +1746,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>805358</t>
+          <t>627671</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>805358</t>
+          <t>627671</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>805358</t>
+          <t>627671</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,17 +1781,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>400891</t>
+          <t>448502</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>400891</t>
+          <t>448502</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>400891</t>
+          <t>448502</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,17 +1816,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>1206249</t>
+          <t>1076174</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1206249</t>
+          <t>1076174</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1206249</t>
+          <t>1076174</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1863,67 +1863,67 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>3092</t>
+          <t>3162</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>867</t>
+          <t>865</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>8664</t>
+          <t>8345</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
+          <t>2,02%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>8336</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>4192</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>15675</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
           <t>2,46%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>8081</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>3852</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>14730</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>2,5%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>11173</t>
+          <t>11498</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6348</t>
+          <t>5998</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>18439</t>
+          <t>18170</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,41%</t>
         </is>
       </c>
     </row>
@@ -1976,32 +1976,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>45239</t>
+          <t>48229</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>31978</t>
+          <t>34477</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>65877</t>
+          <t>66947</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>12,87%</t>
+          <t>11,65%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>18,74%</t>
+          <t>16,17%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2011,32 +2011,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>35850</t>
+          <t>40223</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>23950</t>
+          <t>30599</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>47033</t>
+          <t>52893</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>11,88%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>14,54%</t>
+          <t>15,62%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2046,32 +2046,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>81089</t>
+          <t>88452</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>61343</t>
+          <t>70012</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>103042</t>
+          <t>107165</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>12,01%</t>
+          <t>11,75%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>15,26%</t>
+          <t>14,24%</t>
         </is>
       </c>
     </row>
@@ -2089,32 +2089,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>212075</t>
+          <t>247372</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>191638</t>
+          <t>223236</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>233429</t>
+          <t>272729</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>60,33%</t>
+          <t>59,76%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>54,51%</t>
+          <t>53,93%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>66,4%</t>
+          <t>65,89%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2124,32 +2124,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>204982</t>
+          <t>200470</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>183889</t>
+          <t>183706</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>243069</t>
+          <t>215861</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>63,36%</t>
+          <t>59,2%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>56,84%</t>
+          <t>54,25%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>75,13%</t>
+          <t>63,74%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>417057</t>
+          <t>447842</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>387537</t>
+          <t>419450</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>457876</t>
+          <t>474176</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>61,78%</t>
+          <t>59,51%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>57,41%</t>
+          <t>55,74%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>67,83%</t>
+          <t>63,01%</t>
         </is>
       </c>
     </row>
@@ -2202,32 +2202,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>91141</t>
+          <t>115158</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>74374</t>
+          <t>93322</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>111833</t>
+          <t>139579</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>25,93%</t>
+          <t>27,82%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>21,16%</t>
+          <t>22,55%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>31,81%</t>
+          <t>33,72%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>74614</t>
+          <t>89611</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>49283</t>
+          <t>75053</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>91231</t>
+          <t>104820</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>23,06%</t>
+          <t>26,46%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>15,23%</t>
+          <t>22,16%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>28,2%</t>
+          <t>30,95%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>165755</t>
+          <t>204769</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>137146</t>
+          <t>180210</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>191169</t>
+          <t>234160</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>24,55%</t>
+          <t>27,21%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>20,32%</t>
+          <t>23,95%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>28,32%</t>
+          <t>31,12%</t>
         </is>
       </c>
     </row>
@@ -2315,17 +2315,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>351546</t>
+          <t>413921</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>351546</t>
+          <t>413921</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>351546</t>
+          <t>413921</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2350,17 +2350,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>323528</t>
+          <t>338640</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>323528</t>
+          <t>338640</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>323528</t>
+          <t>338640</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2385,17 +2385,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>675074</t>
+          <t>752561</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>675074</t>
+          <t>752561</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>675074</t>
+          <t>752561</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2432,32 +2432,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>11052</t>
+          <t>16975</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6235</t>
+          <t>8838</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>18657</t>
+          <t>29829</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2467,32 +2467,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>16953</t>
+          <t>13316</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>9023</t>
+          <t>8715</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>37121</t>
+          <t>20476</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2502,32 +2502,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>28005</t>
+          <t>30291</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>17344</t>
+          <t>21226</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>46341</t>
+          <t>44979</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,65%</t>
         </is>
       </c>
     </row>
@@ -2545,32 +2545,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>44755</t>
+          <t>48309</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>33065</t>
+          <t>35567</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>59532</t>
+          <t>63049</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>9,33%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>12,17%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2580,32 +2580,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>44073</t>
+          <t>47364</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>25769</t>
+          <t>36057</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>58161</t>
+          <t>58978</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>10,53%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>13,12%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2615,32 +2615,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>88828</t>
+          <t>95673</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>68215</t>
+          <t>79569</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>110154</t>
+          <t>114749</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>11,86%</t>
         </is>
       </c>
     </row>
@@ -2658,32 +2658,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>259320</t>
+          <t>279291</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>235240</t>
+          <t>254483</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>279458</t>
+          <t>303537</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>54,92%</t>
+          <t>53,93%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>49,82%</t>
+          <t>49,14%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>59,18%</t>
+          <t>58,61%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2693,32 +2693,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>224480</t>
+          <t>252202</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>141580</t>
+          <t>233660</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>268909</t>
+          <t>270495</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>46,61%</t>
+          <t>56,09%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>29,4%</t>
+          <t>51,96%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>55,84%</t>
+          <t>60,15%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2728,32 +2728,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>483800</t>
+          <t>531493</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>376962</t>
+          <t>500033</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>533523</t>
+          <t>561587</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>50,72%</t>
+          <t>54,93%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>39,52%</t>
+          <t>51,68%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>55,94%</t>
+          <t>58,04%</t>
         </is>
       </c>
     </row>
@@ -2771,32 +2771,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>157075</t>
+          <t>173287</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>135765</t>
+          <t>150643</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>180233</t>
+          <t>198838</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>33,26%</t>
+          <t>33,46%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>28,75%</t>
+          <t>29,09%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>38,17%</t>
+          <t>38,4%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>196082</t>
+          <t>136789</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>142158</t>
+          <t>121001</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>303625</t>
+          <t>154586</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>40,72%</t>
+          <t>30,42%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>29,52%</t>
+          <t>26,91%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>63,05%</t>
+          <t>34,38%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>353158</t>
+          <t>310076</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>295871</t>
+          <t>281167</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>490998</t>
+          <t>338061</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>37,03%</t>
+          <t>32,05%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>31,02%</t>
+          <t>29,06%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>51,48%</t>
+          <t>34,94%</t>
         </is>
       </c>
     </row>
@@ -2884,17 +2884,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>472203</t>
+          <t>517861</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>472203</t>
+          <t>517861</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>472203</t>
+          <t>517861</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,17 +2919,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>481588</t>
+          <t>449672</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>481588</t>
+          <t>449672</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>481588</t>
+          <t>449672</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,17 +2954,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>953791</t>
+          <t>967533</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>953791</t>
+          <t>967533</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>953791</t>
+          <t>967533</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -3001,32 +3001,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>46258</t>
+          <t>53465</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>27930</t>
+          <t>38678</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>62642</t>
+          <t>71824</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3036,32 +3036,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>36509</t>
+          <t>35108</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>26185</t>
+          <t>25585</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>61858</t>
+          <t>45610</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3071,32 +3071,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>82767</t>
+          <t>88572</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>61724</t>
+          <t>70269</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>106059</t>
+          <t>110924</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,22%</t>
         </is>
       </c>
     </row>
@@ -3114,102 +3114,102 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>212874</t>
+          <t>226746</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>138148</t>
+          <t>193173</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>261414</t>
+          <t>260955</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
+          <t>11,76%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>10,02%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>13,54%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>233</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>183037</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>161238</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>207654</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>12,1%</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>10,65%</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>13,72%</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>420</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>409783</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>373013</t>
+        </is>
+      </c>
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>450079</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>11,91%</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
           <t>10,84%</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>7,04%</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>13,31%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>233</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>167782</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>139382</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>195893</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>11,48%</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t>9,53%</t>
-        </is>
-      </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>13,4%</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>420</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>380657</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t>301128</t>
-        </is>
-      </c>
-      <c r="T25" s="2" t="inlineStr">
-        <is>
-          <t>433433</t>
-        </is>
-      </c>
-      <c r="U25" s="2" t="inlineStr">
-        <is>
-          <t>11,11%</t>
-        </is>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>8,79%</t>
-        </is>
-      </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>12,65%</t>
+          <t>13,08%</t>
         </is>
       </c>
     </row>
@@ -3227,32 +3227,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>1267240</t>
+          <t>1142692</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1149872</t>
+          <t>1090903</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1541874</t>
+          <t>1185697</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>64,54%</t>
+          <t>59,28%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>58,56%</t>
+          <t>56,59%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>78,53%</t>
+          <t>61,51%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3262,32 +3262,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>838722</t>
+          <t>905658</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>692169</t>
+          <t>869067</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>901657</t>
+          <t>938821</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>57,37%</t>
+          <t>59,85%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>47,35%</t>
+          <t>57,43%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>61,67%</t>
+          <t>62,04%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3297,32 +3297,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>2105962</t>
+          <t>2048350</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1955952</t>
+          <t>1986938</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>2380011</t>
+          <t>2109219</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>61,48%</t>
+          <t>59,53%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>57,1%</t>
+          <t>57,75%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>69,48%</t>
+          <t>61,3%</t>
         </is>
       </c>
     </row>
@@ -3340,32 +3340,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>437044</t>
+          <t>504666</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>276008</t>
+          <t>466686</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>512482</t>
+          <t>552089</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>22,26%</t>
+          <t>26,18%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>14,06%</t>
+          <t>24,21%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>26,1%</t>
+          <t>28,64%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3375,32 +3375,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>418948</t>
+          <t>389479</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>357222</t>
+          <t>357676</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>594142</t>
+          <t>417242</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>28,66%</t>
+          <t>25,74%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>24,43%</t>
+          <t>23,64%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>40,64%</t>
+          <t>27,57%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3410,32 +3410,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>855992</t>
+          <t>894145</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>686233</t>
+          <t>842349</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1003424</t>
+          <t>952063</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>24,99%</t>
+          <t>25,99%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>20,03%</t>
+          <t>24,48%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>29,29%</t>
+          <t>27,67%</t>
         </is>
       </c>
     </row>
@@ -3453,17 +3453,17 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>1963416</t>
+          <t>1927568</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1963416</t>
+          <t>1927568</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1963416</t>
+          <t>1927568</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>1461961</t>
+          <t>1513282</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1461961</t>
+          <t>1513282</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1461961</t>
+          <t>1513282</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3523,17 +3523,17 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>3425377</t>
+          <t>3440851</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3425377</t>
+          <t>3440851</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>3425377</t>
+          <t>3440851</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
